--- a/remove_ttc.xlsx
+++ b/remove_ttc.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Removal log" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -35,7 +35,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,11 +52,6 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,16 +65,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -425,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="23.140625" customWidth="1" min="1" max="1"/>
@@ -457,7 +449,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2401258115</t>
+          <t>2401252331</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -467,7 +459,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2401256705</t>
+          <t>2401252297</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -477,7 +469,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2401251185</t>
+          <t>2401253648</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -487,7 +479,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2401252864</t>
+          <t>2401258115</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -497,7 +489,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2401255649</t>
+          <t>2401256705</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -507,7 +499,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2401252447</t>
+          <t>2401251185</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -517,7 +509,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2401252251</t>
+          <t>2401251467</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -527,7 +519,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2401256842</t>
+          <t>2401252864</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -537,7 +529,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2401256971</t>
+          <t>2401257126</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -547,7 +539,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2401252868</t>
+          <t>2401255649</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -557,10 +549,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2401252447</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2401252251</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2401256842</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2401256754</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2401256971</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2401253088</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2401252868</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2401254000</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2401255565</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>2401251693</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2401256358</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -575,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -609,103 +701,103 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2401258115</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>succeeded</t>
+          <t>2401252331</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2401256705</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>succeeded</t>
+          <t>2401252297</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2401251185</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>succeeded</t>
+          <t>2401253648</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2401252864</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>succeeded</t>
+          <t>2401258115</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2401255649</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>succeeded</t>
+          <t>2401256705</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2401252447</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>succeeded</t>
+          <t>2401251185</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2401252251</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>succeeded</t>
+          <t>2401251467</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2401256842</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>succeeded</t>
+          <t>2401252864</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2401256971</t>
+          <t>2401257126</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -717,24 +809,144 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2401252868</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>succeeded</t>
+          <t>2401255649</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2401252447</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2401252251</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2401256842</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2401256754</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2401256971</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2401253088</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2401252868</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2401254000</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2401255565</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>2401251693</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>succeeded</t>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2401256358</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Failed: not registered or unavailable for removal</t>
         </is>
       </c>
     </row>
